--- a/results/reliability_eval/reliability_eval_09-17-1-test/Llama-3-8B_P101_0_sample_25_tokens_0.1_temp_original_scores_09-17-1-test.xlsx
+++ b/results/reliability_eval/reliability_eval_09-17-1-test/Llama-3-8B_P101_0_sample_25_tokens_0.1_temp_original_scores_09-17-1-test.xlsx
@@ -512,52 +512,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.7217194570135748</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6025641025641025</v>
+        <v>0.575</v>
       </c>
       <c r="C2" t="n">
-        <v>0.285140784109591</v>
+        <v>0.3206333958202679</v>
       </c>
       <c r="D2" t="n">
-        <v>7.473070566164195</v>
+        <v>7.546697260801718</v>
       </c>
       <c r="E2" t="n">
-        <v>7.670938385248423</v>
+        <v>7.378156451556796</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7217194570135748</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6025641025641025</v>
+        <v>0.575</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5347337824881621</v>
+        <v>0.5761107907041858</v>
       </c>
       <c r="I2" t="n">
-        <v>8.35787038581271</v>
+        <v>8.629865999207716</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8921213377558782</v>
+        <v>0.6352031264462098</v>
       </c>
       <c r="K2" t="n">
-        <v>0.995475113122172</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9897435897435898</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02222222222222222</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06365141682948147</v>
+        <v>2.220446049250314e-16</v>
       </c>
       <c r="O2" t="n">
-        <v>1.584962498557113</v>
+        <v>-1.731234192223142e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
